--- a/tams-invest-parent/tams-invest-risk/src/main/resources/tpl/FlowRiskStressTestView002.xlsx
+++ b/tams-invest-parent/tams-invest-risk/src/main/resources/tpl/FlowRiskStressTestView002.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
@@ -16,128 +16,120 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
   <si>
+    <t>组合名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>组合编号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>产品名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>产品规模</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>轻度情景</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重度情景</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中度情景</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>杠杆率</t>
   </si>
   <si>
-    <t>组合名称</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>组合编号</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>产品名称</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>产品规模</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <t>现金余额</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>杠杆率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一级风险缓释后缺口</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>二级风险缓释后缺口</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>二级风险缓释后缺口</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>杠杆率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>申赎净流出（基础）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>现金余额</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>杠杆率</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>资金缺口</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>流动储备/资金缺口</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>资金缺口</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>流动储备/资金缺口</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>流动储备/资金缺口</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>一级流动性储备余额</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>二级流动性储备余额</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>资金流入合计-资产端</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>资金流出合计-资产端</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>轻度情景</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>中度情景</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>重度情景</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>资金缺口</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>一级风险缓释后缺口</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>二级风险缓释后缺口</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>流动储备/资金缺口</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>资金缺口</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>杠杆率</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>资金缺口</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>一级风险缓释后缺口</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>二级风险缓释后缺口</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>流动储备/资金缺口</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -211,16 +203,16 @@
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -531,117 +523,117 @@
   <sheetFormatPr defaultColWidth="18.25" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.15">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
+      <c r="Q1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1" s="4"/>
+      <c r="S1" s="4"/>
+      <c r="T1" s="4"/>
+      <c r="U1" s="4"/>
+      <c r="V1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="2"/>
-      <c r="U1" s="2"/>
-      <c r="V1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="W1" s="2"/>
-      <c r="X1" s="2"/>
-      <c r="Y1" s="2"/>
-      <c r="Z1" s="2"/>
+      <c r="W1" s="4"/>
+      <c r="X1" s="4"/>
+      <c r="Y1" s="4"/>
+      <c r="Z1" s="4"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.15">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
       <c r="L2" s="1" t="s">
         <v>15</v>
       </c>
       <c r="M2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="O2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="P2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="O2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="R2" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="T2" s="1" t="s">
         <v>18</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/tams-invest-parent/tams-invest-risk/src/main/resources/tpl/FlowRiskStressTestView002.xlsx
+++ b/tams-invest-parent/tams-invest-risk/src/main/resources/tpl/FlowRiskStressTestView002.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
@@ -16,120 +16,128 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
   <si>
+    <t>杠杆率</t>
+  </si>
+  <si>
     <t>组合名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>组合编号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>产品名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>产品规模</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>申赎净流出（基础）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>现金余额</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>杠杆率</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>一级流动性储备余额</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>二级流动性储备余额</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>资金流入合计-资产端</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>资金流出合计-资产端</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>轻度情景</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中度情景</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>重度情景</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>中度情景</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>资金缺口</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>一级风险缓释后缺口</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>二级风险缓释后缺口</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>流动储备/资金缺口</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>资金缺口</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>杠杆率</t>
-  </si>
-  <si>
-    <t>现金余额</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>杠杆率</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>资金缺口</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>一级风险缓释后缺口</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>二级风险缓释后缺口</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>二级风险缓释后缺口</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>杠杆率</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>申赎净流出（基础）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>资金缺口</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>流动储备/资金缺口</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>资金缺口</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>流动储备/资金缺口</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>流动储备/资金缺口</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>一级流动性储备余额</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>二级流动性储备余额</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>资金流入合计-资产端</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>资金流出合计-资产端</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>二级风险缓释后缺口</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -203,16 +211,16 @@
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -523,117 +531,117 @@
   <sheetFormatPr defaultColWidth="18.25" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.15">
-      <c r="A1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5" t="s">
+      <c r="A1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="B1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="C1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="D1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
+      <c r="U1" s="2"/>
+      <c r="V1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
-      <c r="Q1" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="R1" s="4"/>
-      <c r="S1" s="4"/>
-      <c r="T1" s="4"/>
-      <c r="U1" s="4"/>
-      <c r="V1" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="W1" s="4"/>
-      <c r="X1" s="4"/>
-      <c r="Y1" s="4"/>
-      <c r="Z1" s="4"/>
+      <c r="W1" s="2"/>
+      <c r="X1" s="2"/>
+      <c r="Y1" s="2"/>
+      <c r="Z1" s="2"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.15">
-      <c r="A2" s="5"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
       <c r="L2" s="1" t="s">
         <v>15</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="O2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q2" s="1" t="s">
+      <c r="S2" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="T2" s="1" t="s">
         <v>18</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="X2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Y2" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="Z2" s="1" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
